--- a/notebooks/Location_Table.xlsx
+++ b/notebooks/Location_Table.xlsx
@@ -863,6 +863,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="51.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
